--- a/engine/adib_study/ADIB_Valuation_Model_10092026.xlsx
+++ b/engine/adib_study/ADIB_Valuation_Model_10092026.xlsx
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>38.5016</v>
+        <v>39.4647</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>-0.112625</v>
+        <v>-0.112375</v>
       </c>
     </row>
     <row r="4">
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>48.2747</v>
+        <v>49.4573</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>0.112625</v>
+        <v>0.112375</v>
       </c>
     </row>
     <row r="5">
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>33.7101</v>
+        <v>34.569</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>-0.223057</v>
+        <v>-0.222486</v>
       </c>
     </row>
     <row r="6">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>53.0662</v>
+        <v>54.3529</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>0.223057</v>
+        <v>0.222486</v>
       </c>
     </row>
     <row r="7">
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>35.1134</v>
+        <v>36.0034</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>-0.190714</v>
+        <v>-0.190225</v>
       </c>
     </row>
     <row r="8">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>51.6629</v>
+        <v>52.9186</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>0.190714</v>
+        <v>0.190225</v>
       </c>
     </row>
     <row r="9">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>37.8479</v>
+        <v>38.7004</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>-0.12769</v>
+        <v>-0.129564</v>
       </c>
     </row>
     <row r="10">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>49.6443</v>
+        <v>50.9691</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>0.144191</v>
+        <v>0.146378</v>
       </c>
     </row>
     <row r="11">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>35.8297</v>
+        <v>36.6044</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>-0.174205</v>
+        <v>-0.176707</v>
       </c>
     </row>
     <row r="12">
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>54.3876</v>
+        <v>55.9735</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.253513</v>
+        <v>0.258936</v>
       </c>
     </row>
     <row r="13">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>44.895</v>
+        <v>46.0776</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0.034729</v>
+        <v>0.036361</v>
       </c>
     </row>
     <row r="14">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>42.1011</v>
+        <v>43.0861</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>-0.029663</v>
+        <v>-0.030924</v>
       </c>
     </row>
     <row r="16">
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>('Income Statement'!E20-'Assumptions'!$B$28)/('Assumptions'!B32-'Assumptions'!$B$28)</f>
+        <f>('Income Statement'!E20-'Assumptions'!$B$31)/('Assumptions'!B35-'Assumptions'!$B$31)</f>
         <v/>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -3189,23 +3189,23 @@
         </is>
       </c>
       <c r="D5" s="11">
-        <f>'Assumptions'!B33</f>
+        <f>'Assumptions'!B36</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>'Assumptions'!C33</f>
+        <f>'Assumptions'!C36</f>
         <v/>
       </c>
       <c r="F5" s="11">
-        <f>'Assumptions'!D33</f>
+        <f>'Assumptions'!D36</f>
         <v/>
       </c>
       <c r="G5" s="11">
-        <f>'Assumptions'!E33</f>
+        <f>'Assumptions'!E36</f>
         <v/>
       </c>
       <c r="H5" s="11">
-        <f>'Assumptions'!F33</f>
+        <f>'Assumptions'!F36</f>
         <v/>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="B9" s="9">
-        <f>1-'Assumptions'!$B$28/B8</f>
+        <f>1-'Assumptions'!$B$31/B8</f>
         <v/>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="B10" s="6">
-        <f>'Income Statement'!I14*(1+'Assumptions'!$B$28)*B9/('Assumptions'!$B$31-'Assumptions'!$B$28)</f>
+        <f>'Income Statement'!I14*(1+'Assumptions'!$B$31)*B9/('Assumptions'!$B$34-'Assumptions'!$B$31)</f>
         <v/>
       </c>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="B17" s="6">
-        <f>('Income Statement'!I14*(1+'Assumptions'!$B$28)-'Assumptions'!$B$19*'Balance Sheet'!G4*'Assumptions'!$B$28)/('Assumptions'!$B$31-'Assumptions'!$B$28)</f>
+        <f>('Income Statement'!I14*(1+'Assumptions'!$B$31)-'Assumptions'!$B$19*'Balance Sheet'!G4*'Assumptions'!$B$31)/('Assumptions'!$B$34-'Assumptions'!$B$31)</f>
         <v/>
       </c>
     </row>
@@ -3413,23 +3413,23 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <f>'Income Statement'!E14-'Assumptions'!B32*'Balance Sheet'!C10</f>
+        <f>'Income Statement'!E14-'Assumptions'!B35*'Balance Sheet'!C10</f>
         <v/>
       </c>
       <c r="E21" s="6">
-        <f>'Income Statement'!F14-'Assumptions'!C32*'Balance Sheet'!D10</f>
+        <f>'Income Statement'!F14-'Assumptions'!C35*'Balance Sheet'!D10</f>
         <v/>
       </c>
       <c r="F21" s="6">
-        <f>'Income Statement'!G14-'Assumptions'!D32*'Balance Sheet'!E10</f>
+        <f>'Income Statement'!G14-'Assumptions'!D35*'Balance Sheet'!E10</f>
         <v/>
       </c>
       <c r="G21" s="6">
-        <f>'Income Statement'!H14-'Assumptions'!E32*'Balance Sheet'!F10</f>
+        <f>'Income Statement'!H14-'Assumptions'!E35*'Balance Sheet'!F10</f>
         <v/>
       </c>
       <c r="H21" s="6">
-        <f>'Income Statement'!I14-'Assumptions'!F32*'Balance Sheet'!G10</f>
+        <f>'Income Statement'!I14-'Assumptions'!F35*'Balance Sheet'!G10</f>
         <v/>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="B24" s="6">
-        <f>(('Income Statement'!I14-'Assumptions'!$B$31*'Balance Sheet'!G10)*(1+'Assumptions'!$B$28)/('Assumptions'!$B$31-'Assumptions'!$B$28))*H5</f>
+        <f>(('Income Statement'!I14-'Assumptions'!$B$34*'Balance Sheet'!G10)*(1+'Assumptions'!$B$31)/('Assumptions'!$B$34-'Assumptions'!$B$31))*H5</f>
         <v/>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Effective tax rate. FY2025 actual 27.92%, FY2024 26.64%, the June 2026 half 29.58%. The Egyptian statutory corporate rate is 22.5%; an Egyptian bank pays materially more because the 20% withholding on treasury-bill income is not creditable and part of its cost base is disallowed. 28.5% sits inside the observed range and above the statutory rate for that reason.</t>
+          <t>Effective tax rate. FY2025 actual 27.92%, FY2024 26.64%, the June 2026 half 29.57%. The Egyptian statutory corporate rate is 22.5%; an Egyptian bank pays materially more because the 20% withholding on treasury-bill income is not creditable and part of its cost base is disallowed. 28.5% sits inside the observed range and above the statutory rate for that reason.</t>
         </is>
       </c>
     </row>
@@ -4067,91 +4067,136 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t xml:space="preserve">   of which the MATURE premium — beta applies to this leg only</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04318</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Terminal growth 7.00% = terminal inflation, ZERO REAL. For a bank in an economy whose private credit is 26% of GDP that is deliberately conservative: it assumes ADIB-Egypt stops taking share and stops participating in credit deepening the moment the explicit window closes. It sits BELOW the 12.50% terminal risk-free rate and equals the inflation inside it, so the terminal cannot grow faster than the money it is discounted in.</t>
+          <t>Damodaran identity: total premium less the country leg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Egypt country premium — charged FLAT, once, never multiplied by beta</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="n">
+        <v>0.051984</v>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>sovereign default spread x the equity-to-bond scaling</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Cost of equity  (= rf − sovereign spread + beta × premium)</t>
-        </is>
-      </c>
-      <c r="B30" s="16">
-        <f>B22-B23+B24*B25</f>
-        <v/>
+          <t>Terminal country premium — charged FLAT and once</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n">
+        <v>0.02682000000000001</v>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>terminal total premium less the SAME mature leg: what normalises is country risk</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of equity</t>
-        </is>
-      </c>
-      <c r="B31" s="16">
-        <f>B26+B24*B27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Cost of equity by year (glide)</t>
-        </is>
-      </c>
-      <c r="B32" s="16">
-        <f>$B$30+($B$31-$B$30)*1/6</f>
-        <v/>
-      </c>
-      <c r="C32" s="16">
-        <f>$B$30+($B$31-$B$30)*2/6</f>
-        <v/>
-      </c>
-      <c r="D32" s="16">
-        <f>$B$30+($B$31-$B$30)*3/6</f>
-        <v/>
-      </c>
-      <c r="E32" s="16">
-        <f>$B$30+($B$31-$B$30)*4/6</f>
-        <v/>
-      </c>
-      <c r="F32" s="16">
-        <f>$B$30+($B$31-$B$30)*5/6</f>
-        <v/>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>Terminal growth 7.00% = terminal inflation, ZERO REAL. For a bank in an economy whose private credit is 26% of GDP that is deliberately conservative: it assumes ADIB-Egypt stops taking share and stops participating in credit deepening the moment the explicit window closes. It sits BELOW the 12.50% terminal risk-free rate and equals the inflation inside it, so the terminal cannot grow faster than the money it is discounted in.</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t>Cost of equity  (= rf − sovereign spread + beta × MATURE premium + country premium, flat)</t>
+        </is>
+      </c>
+      <c r="B33" s="16">
+        <f>B22-B23+B24*B28+B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Terminal cost of equity</t>
+        </is>
+      </c>
+      <c r="B34" s="16">
+        <f>B26+B24*B28+B30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Cost of equity by year (glide)</t>
+        </is>
+      </c>
+      <c r="B35" s="16">
+        <f>$B$33+($B$34-$B$33)*1/6</f>
+        <v/>
+      </c>
+      <c r="C35" s="16">
+        <f>$B$33+($B$34-$B$33)*2/6</f>
+        <v/>
+      </c>
+      <c r="D35" s="16">
+        <f>$B$33+($B$34-$B$33)*3/6</f>
+        <v/>
+      </c>
+      <c r="E35" s="16">
+        <f>$B$33+($B$34-$B$33)*4/6</f>
+        <v/>
+      </c>
+      <c r="F35" s="16">
+        <f>$B$33+($B$34-$B$33)*5/6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B33" s="11">
-        <f>1/(1+B32)</f>
-        <v/>
-      </c>
-      <c r="C33" s="11">
-        <f>B33/(1+C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="11">
-        <f>C33/(1+D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="11">
-        <f>D33/(1+E32)</f>
-        <v/>
-      </c>
-      <c r="F33" s="11">
-        <f>E33/(1+F32)</f>
+      <c r="B36" s="11">
+        <f>1/(1+B35)</f>
+        <v/>
+      </c>
+      <c r="C36" s="11">
+        <f>B36/(1+C35)</f>
+        <v/>
+      </c>
+      <c r="D36" s="11">
+        <f>C36/(1+D35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="11">
+        <f>D36/(1+E35)</f>
+        <v/>
+      </c>
+      <c r="F36" s="11">
+        <f>E36/(1+F35)</f>
         <v/>
       </c>
     </row>
@@ -4595,7 +4640,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>(B16-'Assumptions'!$B$28)/('Assumptions'!$B$31-'Assumptions'!$B$28)</f>
+        <f>(B16-'Assumptions'!$B$31)/('Assumptions'!$B$34-'Assumptions'!$B$31)</f>
         <v/>
       </c>
     </row>
@@ -4673,7 +4718,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>B25/('Assumptions'!$B$30-'Assumptions'!$B$28)/'Summary'!$B$5</f>
+        <f>B25/('Assumptions'!$B$33-'Assumptions'!$B$31)/'Summary'!$B$5</f>
         <v/>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -4807,23 +4852,23 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>'Assumptions'!B32</f>
+        <f>'Assumptions'!B35</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>'Assumptions'!C32</f>
+        <f>'Assumptions'!C35</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>'Assumptions'!D32</f>
+        <f>'Assumptions'!D35</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>'Assumptions'!E32</f>
+        <f>'Assumptions'!E35</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>'Assumptions'!F32</f>
+        <f>'Assumptions'!F35</f>
         <v/>
       </c>
     </row>
@@ -4834,23 +4879,23 @@
         </is>
       </c>
       <c r="B13" s="11">
-        <f>'Assumptions'!B33</f>
+        <f>'Assumptions'!B36</f>
         <v/>
       </c>
       <c r="C13" s="11">
-        <f>'Assumptions'!C33</f>
+        <f>'Assumptions'!C36</f>
         <v/>
       </c>
       <c r="D13" s="11">
-        <f>'Assumptions'!D33</f>
+        <f>'Assumptions'!D36</f>
         <v/>
       </c>
       <c r="E13" s="11">
-        <f>'Assumptions'!E33</f>
+        <f>'Assumptions'!E36</f>
         <v/>
       </c>
       <c r="F13" s="11">
-        <f>'Assumptions'!F33</f>
+        <f>'Assumptions'!F36</f>
         <v/>
       </c>
     </row>
